--- a/dashboard-v2/public/Modelo_Terceirizacao.xlsx
+++ b/dashboard-v2/public/Modelo_Terceirizacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\dashboard-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D10F62B9-00B4-4B60-A6A5-E6591072D173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87178FAB-7FD7-448C-8AF3-7F6222F0CB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{378DDA53-7D95-4973-A83B-63C7FB216C4E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="51">
   <si>
     <t>ISS:</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Valor Líquido</t>
   </si>
   <si>
-    <t>BONIFICAÇÃO</t>
-  </si>
-  <si>
     <t>ADIANTAMENTO</t>
   </si>
   <si>
@@ -194,91 +191,7 @@
     <t>Bertioga</t>
   </si>
   <si>
-    <t>Créditos somente a partir de 02/07 e tudo como antecipações DZM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RELATÓRIO DE PAGAMENTO DA NOTA - </t>
-  </si>
-  <si>
-    <t>Julho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLANILHA PARA SEPARAR POR COMPETÊNCIA NO GC </t>
-  </si>
-  <si>
-    <t>LANÇAMENTO GC</t>
-  </si>
-  <si>
-    <t>A cobrir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vencimento </t>
-  </si>
-  <si>
-    <t>HOLERITE</t>
-  </si>
-  <si>
-    <t>SEGURO</t>
-  </si>
-  <si>
-    <t>FGTS</t>
-  </si>
-  <si>
-    <t>PERFIL</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Banco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Competência </t>
-  </si>
-  <si>
-    <t>Omie.Cash</t>
-  </si>
-  <si>
-    <t>Chiller</t>
-  </si>
-  <si>
-    <t>Praia Grande</t>
-  </si>
-  <si>
-    <t>Ybox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bateu </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Bateu </t>
-  </si>
-  <si>
-    <t>A compensar</t>
-  </si>
-  <si>
-    <t>A descontar</t>
-  </si>
-  <si>
-    <t>Saldo</t>
-  </si>
-  <si>
-    <t>ANTECIPAÇÕES - INTERMEDIAÇÃO</t>
-  </si>
-  <si>
-    <t>&lt;=======</t>
-  </si>
-  <si>
-    <t>Preencher</t>
-  </si>
-  <si>
-    <t>Faltando</t>
-  </si>
-  <si>
-    <t>Saldo Créditos DZM na MarBR</t>
+    <t>Bônus</t>
   </si>
 </sst>
 </file>
@@ -288,24 +201,10 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -334,32 +233,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF467886"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0E2841"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="11">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -402,26 +277,8 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8E8E8"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="35">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -682,373 +539,67 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="3" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="3" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="3" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="3" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="1" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="1" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="1" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="8" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1383,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFCA590A-D0A7-424A-B548-17A931DC9594}">
-  <dimension ref="A1:AA65"/>
+  <dimension ref="A1:AA28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
@@ -1563,40 +1114,40 @@
         <v>8</v>
       </c>
       <c r="G6" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="I6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="J6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="K6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="L6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="M6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="N6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="O6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="P6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="P6" s="11" t="s">
+      <c r="Q6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="Q6" s="12" t="s">
+      <c r="R6" s="13" t="s">
         <v>19</v>
-      </c>
-      <c r="R6" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="S6" s="14"/>
       <c r="T6" s="14"/>
@@ -1611,10 +1162,10 @@
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="15"/>
       <c r="B7" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>21</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>22</v>
       </c>
       <c r="D7" s="17">
         <v>7500</v>
@@ -1651,13 +1202,13 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="C8" s="24" t="s">
         <v>24</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>25</v>
       </c>
       <c r="D8" s="25">
         <v>3037.67</v>
@@ -1673,10 +1224,10 @@
         <v>739.92</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K8" s="26">
         <v>273</v>
@@ -1714,13 +1265,13 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="C9" s="24" t="s">
         <v>28</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>29</v>
       </c>
       <c r="D9" s="25">
         <v>1700</v>
@@ -1761,13 +1312,13 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="24" t="s">
         <v>30</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>31</v>
       </c>
       <c r="D10" s="25">
         <v>2022.91</v>
@@ -1785,7 +1336,7 @@
         <v>739.92</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J10" s="29">
         <v>320</v>
@@ -1826,13 +1377,13 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" s="31">
         <v>1820.13</v>
@@ -1848,7 +1399,7 @@
         <v>690.6</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J11" s="30"/>
       <c r="K11" s="30"/>
@@ -1885,13 +1436,13 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" s="25">
         <v>2124.7600000000002</v>
@@ -1948,13 +1499,13 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" s="25">
         <v>2182.5300000000002</v>
@@ -1972,7 +1523,7 @@
         <v>739.92</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J13" s="26">
         <v>320</v>
@@ -2013,13 +1564,13 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" s="25">
         <v>1000</v>
@@ -2062,13 +1613,13 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" s="25">
         <v>1917.35</v>
@@ -2084,7 +1635,7 @@
         <v>739.92</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J15" s="26">
         <v>820</v>
@@ -2125,13 +1676,13 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" s="25">
         <v>1849.81</v>
@@ -2147,7 +1698,7 @@
         <v>739.92</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J16" s="26">
         <v>320</v>
@@ -2188,13 +1739,13 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" s="25">
         <v>1849.81</v>
@@ -2210,7 +1761,7 @@
         <v>739.92</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J17" s="26">
         <v>320</v>
@@ -2251,13 +1802,13 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" s="25">
         <v>1849.81</v>
@@ -2273,7 +1824,7 @@
         <v>739.92</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J18" s="26">
         <v>320</v>
@@ -2314,13 +1865,13 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" s="25">
         <v>1951.09</v>
@@ -2336,7 +1887,7 @@
         <v>739.92</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J19" s="26">
         <v>320</v>
@@ -2354,7 +1905,7 @@
         <v>128.55000000000001</v>
       </c>
       <c r="O19" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P19" s="20">
         <v>2541.36</v>
@@ -2377,13 +1928,13 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20" s="25">
         <v>1849.41</v>
@@ -2399,7 +1950,7 @@
         <v>739.76</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J20" s="26">
         <v>320</v>
@@ -2440,13 +1991,13 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D21" s="25">
         <v>2349.81</v>
@@ -2462,7 +2013,7 @@
         <v>739.92</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J21" s="26">
         <v>320</v>
@@ -2503,13 +2054,13 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D22" s="25">
         <v>2108.7800000000002</v>
@@ -2568,13 +2119,13 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" s="25">
         <v>2061.6799999999998</v>
@@ -2631,13 +2182,13 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" s="25">
         <v>1500</v>
@@ -2680,13 +2231,13 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D25" s="25">
         <v>1849.81</v>
@@ -2702,7 +2253,7 @@
         <v>739.92</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J25" s="26">
         <v>320</v>
@@ -2743,13 +2294,13 @@
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" s="25">
         <v>1000</v>
@@ -2793,10 +2344,10 @@
     <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" s="33"/>
       <c r="B27" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="35" t="s">
         <v>49</v>
-      </c>
-      <c r="C27" s="35" t="s">
-        <v>50</v>
       </c>
       <c r="D27" s="31">
         <v>2027.88</v>
@@ -2838,7 +2389,7 @@
         <v>15</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="38">
@@ -2896,1469 +2447,7 @@
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-      <c r="Z29" s="1"/>
-      <c r="AA29" s="1"/>
-    </row>
-    <row r="30" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
-      <c r="AA30" s="1"/>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A31" s="75" t="s">
-        <v>52</v>
-      </c>
-      <c r="B31" s="76"/>
-      <c r="C31" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="77" t="s">
-        <v>54</v>
-      </c>
-      <c r="F31" s="78"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="78"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="78"/>
-      <c r="K31" s="78"/>
-      <c r="L31" s="78"/>
-      <c r="M31" s="78"/>
-      <c r="N31" s="78"/>
-      <c r="O31" s="78"/>
-      <c r="P31" s="78"/>
-      <c r="Q31" s="78"/>
-      <c r="R31" s="78"/>
-      <c r="S31" s="78"/>
-      <c r="T31" s="79"/>
-      <c r="U31" s="80" t="s">
-        <v>55</v>
-      </c>
-      <c r="V31" s="81"/>
-      <c r="W31" s="81"/>
-      <c r="X31" s="81"/>
-      <c r="Y31" s="81"/>
-      <c r="Z31" s="81"/>
-      <c r="AA31" s="81"/>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A32" s="41"/>
-      <c r="B32" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="43">
-        <v>66408.899999999994</v>
-      </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J32" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="K32" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="R32" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-      <c r="Z32" s="1"/>
-      <c r="AA32" s="1"/>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A33" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" s="46" t="s">
-        <v>63</v>
-      </c>
-      <c r="C33" s="47" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F33" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="G33" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="H33" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="I33" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="J33" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="K33" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="L33" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="M33" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="N33" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="O33" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="R33" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
-      <c r="W33" s="1"/>
-      <c r="X33" s="1"/>
-      <c r="Y33" s="1"/>
-      <c r="Z33" s="1"/>
-      <c r="AA33" s="1"/>
-    </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A34" s="45"/>
-      <c r="B34" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="C34" s="49"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="F34" s="25">
-        <v>25870.34</v>
-      </c>
-      <c r="G34" s="25">
-        <v>1000</v>
-      </c>
-      <c r="H34" s="25">
-        <v>10494.39</v>
-      </c>
-      <c r="I34" s="25">
-        <v>1645.88</v>
-      </c>
-      <c r="J34" s="25">
-        <v>3840</v>
-      </c>
-      <c r="K34" s="25">
-        <v>5086.3</v>
-      </c>
-      <c r="L34" s="25">
-        <v>194.48</v>
-      </c>
-      <c r="M34" s="25">
-        <v>1884.32</v>
-      </c>
-      <c r="N34" s="25">
-        <v>1799.94</v>
-      </c>
-      <c r="O34" s="25">
-        <v>547.20000000000005</v>
-      </c>
-      <c r="P34" s="25">
-        <v>37147.39</v>
-      </c>
-      <c r="Q34" s="25">
-        <v>5007.47</v>
-      </c>
-      <c r="R34" s="25">
-        <v>42154.86</v>
-      </c>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="1"/>
-      <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
-      <c r="Z34" s="1"/>
-      <c r="AA34" s="1"/>
-    </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A35" s="45"/>
-      <c r="B35" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="C35" s="49"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="F35" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="G35" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="H35" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="I35" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J35" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="K35" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="O35" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="P35" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q35" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="R35" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
-      <c r="W35" s="1"/>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
-      <c r="Z35" s="1"/>
-      <c r="AA35" s="1"/>
-    </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A36" s="45"/>
-      <c r="B36" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" s="49"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="F36" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="G36" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="H36" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="I36" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J36" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="K36" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="L36" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="M36" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="N36" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="O36" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="P36" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q36" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="R36" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
-      <c r="W36" s="1"/>
-      <c r="X36" s="1"/>
-      <c r="Y36" s="1"/>
-      <c r="Z36" s="1"/>
-      <c r="AA36" s="1"/>
-    </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A37" s="45"/>
-      <c r="B37" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" s="49"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="F37" s="25">
-        <v>7117.35</v>
-      </c>
-      <c r="G37" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="H37" s="25">
-        <v>739.92</v>
-      </c>
-      <c r="I37" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J37" s="25">
-        <v>820</v>
-      </c>
-      <c r="K37" s="25">
-        <v>1138</v>
-      </c>
-      <c r="L37" s="25">
-        <v>74.8</v>
-      </c>
-      <c r="M37" s="25">
-        <v>147.97999999999999</v>
-      </c>
-      <c r="N37" s="25">
-        <v>142.16</v>
-      </c>
-      <c r="O37" s="25">
-        <v>45.6</v>
-      </c>
-      <c r="P37" s="25">
-        <v>9232.74</v>
-      </c>
-      <c r="Q37" s="25">
-        <v>1244.57</v>
-      </c>
-      <c r="R37" s="25">
-        <v>10477.31</v>
-      </c>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="1"/>
-      <c r="X37" s="1"/>
-      <c r="Y37" s="1"/>
-      <c r="Z37" s="1"/>
-      <c r="AA37" s="1"/>
-    </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A38" s="45"/>
-      <c r="B38" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="C38" s="49"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="F38" s="25">
-        <v>2027.88</v>
-      </c>
-      <c r="G38" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="H38" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="I38" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J38" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="K38" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="L38" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="M38" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="N38" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="O38" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="P38" s="25">
-        <v>2027.88</v>
-      </c>
-      <c r="Q38" s="25">
-        <v>273.36</v>
-      </c>
-      <c r="R38" s="25">
-        <v>2301.2399999999998</v>
-      </c>
-      <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
-      <c r="Z38" s="1"/>
-      <c r="AA38" s="1"/>
-    </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A39" s="45"/>
-      <c r="B39" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="C39" s="49"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="F39" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="G39" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="H39" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="I39" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J39" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="K39" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="M39" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="N39" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="O39" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="P39" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q39" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="R39" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
-      <c r="Z39" s="1"/>
-      <c r="AA39" s="1"/>
-    </row>
-    <row r="40" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="45"/>
-      <c r="B40" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="C40" s="49"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="25">
-        <v>3037.67</v>
-      </c>
-      <c r="G40" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="H40" s="25">
-        <v>739.92</v>
-      </c>
-      <c r="I40" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J40" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="K40" s="25">
-        <v>273</v>
-      </c>
-      <c r="L40" s="25">
-        <v>14.96</v>
-      </c>
-      <c r="M40" s="25">
-        <v>243.01</v>
-      </c>
-      <c r="N40" s="25">
-        <v>253.1</v>
-      </c>
-      <c r="O40" s="25">
-        <v>45.6</v>
-      </c>
-      <c r="P40" s="25">
-        <v>3503.25</v>
-      </c>
-      <c r="Q40" s="25">
-        <v>472.24</v>
-      </c>
-      <c r="R40" s="25">
-        <v>3975.49</v>
-      </c>
-      <c r="S40" s="1"/>
-      <c r="T40" s="1"/>
-      <c r="U40" s="1"/>
-      <c r="V40" s="1"/>
-      <c r="W40" s="1"/>
-      <c r="X40" s="1"/>
-      <c r="Y40" s="1"/>
-      <c r="Z40" s="1"/>
-      <c r="AA40" s="1"/>
-    </row>
-    <row r="41" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="45"/>
-      <c r="B41" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" s="50"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="51">
-        <v>38053.24</v>
-      </c>
-      <c r="G41" s="52">
-        <v>1000</v>
-      </c>
-      <c r="H41" s="52">
-        <v>11974.23</v>
-      </c>
-      <c r="I41" s="52">
-        <v>1645.88</v>
-      </c>
-      <c r="J41" s="52">
-        <v>4660</v>
-      </c>
-      <c r="K41" s="52">
-        <v>6497.3</v>
-      </c>
-      <c r="L41" s="52">
-        <v>284.24</v>
-      </c>
-      <c r="M41" s="52">
-        <v>2275.31</v>
-      </c>
-      <c r="N41" s="52">
-        <v>2195.1999999999998</v>
-      </c>
-      <c r="O41" s="52">
-        <v>638.4</v>
-      </c>
-      <c r="P41" s="52">
-        <v>59411.26</v>
-      </c>
-      <c r="Q41" s="52">
-        <v>6997.64</v>
-      </c>
-      <c r="R41" s="52">
-        <v>66408.899999999994</v>
-      </c>
-      <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
-      <c r="U41" s="1"/>
-      <c r="V41" s="1"/>
-      <c r="W41" s="1"/>
-      <c r="X41" s="1"/>
-      <c r="Y41" s="1"/>
-      <c r="Z41" s="1"/>
-      <c r="AA41" s="1"/>
-    </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A42" s="45"/>
-      <c r="B42" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="C42" s="50"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="G42" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="H42" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="I42" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="J42" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="K42" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="L42" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="M42" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="N42" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="O42" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="P42" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q42" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="R42" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
-      <c r="W42" s="1"/>
-      <c r="X42" s="1"/>
-      <c r="Y42" s="1"/>
-      <c r="Z42" s="1"/>
-      <c r="AA42" s="1"/>
-    </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A43" s="54"/>
-      <c r="B43" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="C43" s="50"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
-      <c r="X43" s="1"/>
-      <c r="Y43" s="1"/>
-      <c r="Z43" s="1"/>
-      <c r="AA43" s="1"/>
-    </row>
-    <row r="44" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="56"/>
-      <c r="B44" s="57" t="s">
-        <v>18</v>
-      </c>
-      <c r="C44" s="58" t="s">
-        <v>41</v>
-      </c>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-      <c r="X44" s="1"/>
-      <c r="Y44" s="1"/>
-      <c r="Z44" s="1"/>
-      <c r="AA44" s="1"/>
-    </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A45" s="1"/>
-      <c r="B45" s="59" t="s">
-        <v>72</v>
-      </c>
-      <c r="C45" s="60"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
-      <c r="Q45" s="1"/>
-      <c r="R45" s="1"/>
-      <c r="S45" s="1"/>
-      <c r="T45" s="1"/>
-      <c r="U45" s="1"/>
-      <c r="V45" s="1"/>
-      <c r="W45" s="1"/>
-      <c r="X45" s="1"/>
-      <c r="Y45" s="1"/>
-      <c r="Z45" s="1"/>
-      <c r="AA45" s="1"/>
-    </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
-      <c r="V46" s="1"/>
-      <c r="W46" s="1"/>
-      <c r="X46" s="1"/>
-      <c r="Y46" s="1"/>
-      <c r="Z46" s="1"/>
-      <c r="AA46" s="1"/>
-    </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-      <c r="Q47" s="1"/>
-      <c r="R47" s="1"/>
-      <c r="S47" s="1"/>
-      <c r="T47" s="1"/>
-      <c r="U47" s="1"/>
-      <c r="V47" s="1"/>
-      <c r="W47" s="1"/>
-      <c r="X47" s="1"/>
-      <c r="Y47" s="1"/>
-      <c r="Z47" s="1"/>
-      <c r="AA47" s="1"/>
-    </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C48" s="6">
-        <v>66408.899999999994</v>
-      </c>
-      <c r="D48" s="1"/>
-      <c r="E48" s="82"/>
-      <c r="F48" s="82"/>
-      <c r="G48" s="82"/>
-      <c r="H48" s="82"/>
-      <c r="I48" s="82"/>
-      <c r="J48" s="82"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-      <c r="Q48" s="1"/>
-      <c r="R48" s="1"/>
-      <c r="S48" s="1"/>
-      <c r="T48" s="1"/>
-      <c r="U48" s="1"/>
-      <c r="V48" s="1"/>
-      <c r="W48" s="1"/>
-      <c r="X48" s="1"/>
-      <c r="Y48" s="1"/>
-      <c r="Z48" s="1"/>
-      <c r="AA48" s="1"/>
-    </row>
-    <row r="49" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
-      <c r="P49" s="1"/>
-      <c r="Q49" s="1"/>
-      <c r="R49" s="1"/>
-      <c r="S49" s="1"/>
-      <c r="T49" s="1"/>
-      <c r="U49" s="1"/>
-      <c r="V49" s="1"/>
-      <c r="W49" s="1"/>
-      <c r="X49" s="1"/>
-      <c r="Y49" s="1"/>
-      <c r="Z49" s="1"/>
-      <c r="AA49" s="1"/>
-    </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A50" s="83" t="s">
-        <v>75</v>
-      </c>
-      <c r="B50" s="84"/>
-      <c r="C50" s="61" t="s">
-        <v>53</v>
-      </c>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
-      <c r="R50" s="1"/>
-      <c r="S50" s="1"/>
-      <c r="T50" s="1"/>
-      <c r="U50" s="1"/>
-      <c r="V50" s="1"/>
-      <c r="W50" s="1"/>
-      <c r="X50" s="1"/>
-      <c r="Y50" s="1"/>
-      <c r="Z50" s="1"/>
-      <c r="AA50" s="1"/>
-    </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A51" s="41"/>
-      <c r="B51" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51" s="42"/>
-      <c r="D51" s="62" t="s">
-        <v>76</v>
-      </c>
-      <c r="E51" s="62" t="s">
-        <v>77</v>
-      </c>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
-      <c r="P51" s="1"/>
-      <c r="Q51" s="1"/>
-      <c r="R51" s="1"/>
-      <c r="S51" s="1"/>
-      <c r="T51" s="1"/>
-      <c r="U51" s="1"/>
-      <c r="V51" s="1"/>
-      <c r="W51" s="1"/>
-      <c r="X51" s="1"/>
-      <c r="Y51" s="1"/>
-      <c r="Z51" s="1"/>
-      <c r="AA51" s="1"/>
-    </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A52" s="63" t="s">
-        <v>62</v>
-      </c>
-      <c r="B52" s="64" t="s">
-        <v>63</v>
-      </c>
-      <c r="C52" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1"/>
-      <c r="R52" s="1"/>
-      <c r="S52" s="1"/>
-      <c r="T52" s="1"/>
-      <c r="U52" s="1"/>
-      <c r="V52" s="1"/>
-      <c r="W52" s="1"/>
-      <c r="X52" s="1"/>
-      <c r="Y52" s="1"/>
-      <c r="Z52" s="1"/>
-      <c r="AA52" s="1"/>
-    </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A53" s="63"/>
-      <c r="B53" s="66"/>
-      <c r="C53" s="67"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
-      <c r="P53" s="1"/>
-      <c r="Q53" s="1"/>
-      <c r="R53" s="1"/>
-      <c r="S53" s="1"/>
-      <c r="T53" s="1"/>
-      <c r="U53" s="1"/>
-      <c r="V53" s="1"/>
-      <c r="W53" s="1"/>
-      <c r="X53" s="1"/>
-      <c r="Y53" s="1"/>
-      <c r="Z53" s="1"/>
-      <c r="AA53" s="1"/>
-    </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A54" s="63"/>
-      <c r="B54" s="66"/>
-      <c r="C54" s="67"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
-      <c r="R54" s="1"/>
-      <c r="S54" s="1"/>
-      <c r="T54" s="1"/>
-      <c r="U54" s="1"/>
-      <c r="V54" s="1"/>
-      <c r="W54" s="1"/>
-      <c r="X54" s="1"/>
-      <c r="Y54" s="1"/>
-      <c r="Z54" s="1"/>
-      <c r="AA54" s="1"/>
-    </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A55" s="63"/>
-      <c r="B55" s="66"/>
-      <c r="C55" s="67"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
-      <c r="P55" s="1"/>
-      <c r="Q55" s="1"/>
-      <c r="R55" s="1"/>
-      <c r="S55" s="1"/>
-      <c r="T55" s="1"/>
-      <c r="U55" s="1"/>
-      <c r="V55" s="1"/>
-      <c r="W55" s="1"/>
-      <c r="X55" s="1"/>
-      <c r="Y55" s="1"/>
-      <c r="Z55" s="1"/>
-      <c r="AA55" s="1"/>
-    </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A56" s="63"/>
-      <c r="B56" s="66"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
-      <c r="Q56" s="1"/>
-      <c r="R56" s="1"/>
-      <c r="S56" s="1"/>
-      <c r="T56" s="1"/>
-      <c r="U56" s="1"/>
-      <c r="V56" s="1"/>
-      <c r="W56" s="1"/>
-      <c r="X56" s="1"/>
-      <c r="Y56" s="1"/>
-      <c r="Z56" s="1"/>
-      <c r="AA56" s="1"/>
-    </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A57" s="63"/>
-      <c r="B57" s="66"/>
-      <c r="C57" s="67"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
-      <c r="R57" s="1"/>
-      <c r="S57" s="1"/>
-      <c r="T57" s="1"/>
-      <c r="U57" s="1"/>
-      <c r="V57" s="1"/>
-      <c r="W57" s="1"/>
-      <c r="X57" s="1"/>
-      <c r="Y57" s="1"/>
-      <c r="Z57" s="1"/>
-      <c r="AA57" s="1"/>
-    </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A58" s="63"/>
-      <c r="B58" s="66"/>
-      <c r="C58" s="67"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
-      <c r="R58" s="1"/>
-      <c r="S58" s="1"/>
-      <c r="T58" s="1"/>
-      <c r="U58" s="1"/>
-      <c r="V58" s="1"/>
-      <c r="W58" s="1"/>
-      <c r="X58" s="1"/>
-      <c r="Y58" s="1"/>
-      <c r="Z58" s="1"/>
-      <c r="AA58" s="1"/>
-    </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A59" s="63"/>
-      <c r="B59" s="66"/>
-      <c r="C59" s="68"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1"/>
-      <c r="Q59" s="1"/>
-      <c r="R59" s="1"/>
-      <c r="S59" s="1"/>
-      <c r="T59" s="1"/>
-      <c r="U59" s="1"/>
-      <c r="V59" s="1"/>
-      <c r="W59" s="1"/>
-      <c r="X59" s="1"/>
-      <c r="Y59" s="1"/>
-      <c r="Z59" s="1"/>
-      <c r="AA59" s="1"/>
-    </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A60" s="63"/>
-      <c r="B60" s="66"/>
-      <c r="C60" s="68"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
-      <c r="R60" s="1"/>
-      <c r="S60" s="1"/>
-      <c r="T60" s="1"/>
-      <c r="U60" s="1"/>
-      <c r="V60" s="1"/>
-      <c r="W60" s="1"/>
-      <c r="X60" s="1"/>
-      <c r="Y60" s="1"/>
-      <c r="Z60" s="1"/>
-      <c r="AA60" s="1"/>
-    </row>
-    <row r="61" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="69"/>
-      <c r="B61" s="70" t="s">
-        <v>18</v>
-      </c>
-      <c r="C61" s="71" t="s">
-        <v>41</v>
-      </c>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
-      <c r="R61" s="1"/>
-      <c r="S61" s="1"/>
-      <c r="T61" s="1"/>
-      <c r="U61" s="1"/>
-      <c r="V61" s="1"/>
-      <c r="W61" s="1"/>
-      <c r="X61" s="1"/>
-      <c r="Y61" s="1"/>
-      <c r="Z61" s="1"/>
-      <c r="AA61" s="1"/>
-    </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
-      <c r="R62" s="1"/>
-      <c r="S62" s="1"/>
-      <c r="T62" s="1"/>
-      <c r="U62" s="1"/>
-      <c r="V62" s="1"/>
-      <c r="W62" s="1"/>
-      <c r="X62" s="1"/>
-      <c r="Y62" s="1"/>
-      <c r="Z62" s="1"/>
-      <c r="AA62" s="1"/>
-    </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A63" s="1"/>
-      <c r="B63" s="72" t="s">
-        <v>78</v>
-      </c>
-      <c r="C63" s="73" t="s">
-        <v>41</v>
-      </c>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="1"/>
-      <c r="M63" s="1"/>
-      <c r="N63" s="1"/>
-      <c r="O63" s="1"/>
-      <c r="P63" s="1"/>
-      <c r="Q63" s="1"/>
-      <c r="R63" s="1"/>
-      <c r="S63" s="1"/>
-      <c r="T63" s="1"/>
-      <c r="U63" s="1"/>
-      <c r="V63" s="1"/>
-      <c r="W63" s="1"/>
-      <c r="X63" s="1"/>
-      <c r="Y63" s="1"/>
-      <c r="Z63" s="1"/>
-      <c r="AA63" s="1"/>
-    </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A64" s="1"/>
-      <c r="B64" s="72"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
-      <c r="P64" s="1"/>
-      <c r="Q64" s="1"/>
-      <c r="R64" s="1"/>
-      <c r="S64" s="1"/>
-      <c r="T64" s="1"/>
-      <c r="U64" s="1"/>
-      <c r="V64" s="1"/>
-      <c r="W64" s="1"/>
-      <c r="X64" s="1"/>
-      <c r="Y64" s="1"/>
-      <c r="Z64" s="1"/>
-      <c r="AA64" s="1"/>
-    </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A65" s="1"/>
-      <c r="B65" s="72" t="s">
-        <v>79</v>
-      </c>
-      <c r="C65" s="74"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="1"/>
-      <c r="M65" s="1"/>
-      <c r="N65" s="1"/>
-      <c r="O65" s="1"/>
-      <c r="P65" s="1"/>
-      <c r="Q65" s="1"/>
-      <c r="R65" s="1"/>
-      <c r="S65" s="1"/>
-      <c r="T65" s="1"/>
-      <c r="U65" s="1"/>
-      <c r="V65" s="1"/>
-      <c r="W65" s="1"/>
-      <c r="X65" s="1"/>
-      <c r="Y65" s="1"/>
-      <c r="Z65" s="1"/>
-      <c r="AA65" s="1"/>
-    </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="E31:T31"/>
-    <mergeCell ref="U31:AA31"/>
-    <mergeCell ref="E48:J48"/>
-    <mergeCell ref="A50:B50"/>
-  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>